--- a/InputData/endo-learn/FoTOMRAEL/Frac of Tech Outside Modeled Region Affecting Endo Learning.xlsx
+++ b/InputData/endo-learn/FoTOMRAEL/Frac of Tech Outside Modeled Region Affecting Endo Learning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\ctrl-settings\FoTOMRAEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\MA\endo-learn\FoTOMRAEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D1A431-AF32-4B88-8B24-231C99A9E877}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D79B0F1A-84F3-4F33-95BE-3C39C9B82D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>About</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>onshore wind, offshore wind, solar PV, batteries, and CCS.</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
   </si>
 </sst>
 </file>
@@ -167,16 +170,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -458,18 +461,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="6">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -477,43 +486,43 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -586,10 +595,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -597,8 +606,8 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5">
-        <v>0.25</v>
+      <c r="B2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
